--- a/sample_data/wedstrijd-data-2026-09-12.xlsx
+++ b/sample_data/wedstrijd-data-2026-09-12.xlsx
@@ -1477,10 +1477,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>323.260144</v>
+        <v>329.864643</v>
       </c>
       <c r="D21" t="n">
-        <v>203.226016</v>
+        <v>197.119231</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>303.338308</v>
+        <v>330.171561</v>
       </c>
       <c r="D32" t="n">
-        <v>221.952582</v>
+        <v>197.453269</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>

--- a/sample_data/wedstrijd-data-2026-09-12.xlsx
+++ b/sample_data/wedstrijd-data-2026-09-12.xlsx
@@ -1078,10 +1078,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>225.424057</v>
+        <v>253.249209</v>
       </c>
       <c r="D2" t="n">
-        <v>326.180349</v>
+        <v>367.12068</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>373.197638</v>
+        <v>419.263178</v>
       </c>
       <c r="D3" t="n">
-        <v>257.319829</v>
+        <v>289.617174</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>482.388608</v>
+        <v>541.932104</v>
       </c>
       <c r="D4" t="n">
-        <v>154.57573</v>
+        <v>173.977211</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>419.573807</v>
+        <v>471.363776</v>
       </c>
       <c r="D5" t="n">
-        <v>276.264358</v>
+        <v>310.939514</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>392.90014</v>
+        <v>441.397652</v>
       </c>
       <c r="D6" t="n">
-        <v>154.035082</v>
+        <v>173.368703</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>431.504974</v>
+        <v>484.767663</v>
       </c>
       <c r="D7" t="n">
-        <v>304.389578</v>
+        <v>342.594854</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>124.674038</v>
+        <v>140.063141</v>
       </c>
       <c r="D8" t="n">
-        <v>283.009717</v>
+        <v>318.531512</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>424.913208</v>
+        <v>477.362244</v>
       </c>
       <c r="D9" t="n">
-        <v>261.049288</v>
+        <v>293.814734</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>161.005993</v>
+        <v>180.879721</v>
       </c>
       <c r="D10" t="n">
-        <v>189.590387</v>
+        <v>213.386711</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>465.296533</v>
+        <v>522.730273</v>
       </c>
       <c r="D11" t="n">
-        <v>200.050593</v>
+        <v>225.159824</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>69.956148</v>
+        <v>78.591165</v>
       </c>
       <c r="D12" t="n">
-        <v>237.40575</v>
+        <v>267.203591</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>308.324244</v>
+        <v>346.382156</v>
       </c>
       <c r="D13" t="n">
-        <v>327.275696</v>
+        <v>368.35351</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>63.316667</v>
+        <v>71.132141</v>
       </c>
       <c r="D14" t="n">
-        <v>313.989665</v>
+        <v>353.39989</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>166.060505</v>
+        <v>186.558134</v>
       </c>
       <c r="D15" t="n">
-        <v>278.408519</v>
+        <v>313.352798</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>485.651771</v>
+        <v>545.598054</v>
       </c>
       <c r="D16" t="n">
-        <v>305.833293</v>
+        <v>344.219777</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>151.135512</v>
+        <v>169.790879</v>
       </c>
       <c r="D17" t="n">
-        <v>182.758048</v>
+        <v>205.696816</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>295.432308</v>
+        <v>331.898907</v>
       </c>
       <c r="D18" t="n">
-        <v>141.036639</v>
+        <v>158.738768</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>96.09379800000001</v>
+        <v>107.955108</v>
       </c>
       <c r="D19" t="n">
-        <v>168.948522</v>
+        <v>190.153995</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>166.440031</v>
+        <v>186.984507</v>
       </c>
       <c r="D20" t="n">
-        <v>164.333344</v>
+        <v>184.959546</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>329.864643</v>
+        <v>370.581387</v>
       </c>
       <c r="D21" t="n">
-        <v>197.119231</v>
+        <v>221.860534</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>458.70884</v>
+        <v>515.32943</v>
       </c>
       <c r="D22" t="n">
-        <v>322.771812</v>
+        <v>363.284323</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>160.413689</v>
+        <v>180.214305</v>
       </c>
       <c r="D23" t="n">
-        <v>166.111639</v>
+        <v>186.961043</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>93.671475</v>
+        <v>105.233786</v>
       </c>
       <c r="D24" t="n">
-        <v>118.525524</v>
+        <v>133.402184</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>479.144682</v>
+        <v>538.287765</v>
       </c>
       <c r="D25" t="n">
-        <v>322.048576</v>
+        <v>362.470311</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>391.071858</v>
+        <v>439.343698</v>
       </c>
       <c r="D26" t="n">
-        <v>250.958222</v>
+        <v>282.457093</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>115.656344</v>
+        <v>129.932351</v>
       </c>
       <c r="D27" t="n">
-        <v>206.708039</v>
+        <v>232.652875</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>369.864842</v>
+        <v>415.518999</v>
       </c>
       <c r="D28" t="n">
-        <v>247.700318</v>
+        <v>278.790276</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>368.868924</v>
+        <v>414.400151</v>
       </c>
       <c r="D29" t="n">
-        <v>326.775331</v>
+        <v>367.790341</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>204.207962</v>
+        <v>229.414311</v>
       </c>
       <c r="D30" t="n">
-        <v>195.810094</v>
+        <v>220.387081</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>8</v>
       </c>
       <c r="C31" t="n">
-        <v>147.261496</v>
+        <v>165.438675</v>
       </c>
       <c r="D31" t="n">
-        <v>258.201714</v>
+        <v>290.609748</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>330.171561</v>
+        <v>370.92619</v>
       </c>
       <c r="D32" t="n">
-        <v>197.453269</v>
+        <v>222.236498</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>474.12314</v>
+        <v>532.64639</v>
       </c>
       <c r="D33" t="n">
-        <v>205.869014</v>
+        <v>231.70854</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>107.465832</v>
+        <v>120.730845</v>
       </c>
       <c r="D34" t="n">
-        <v>168.409809</v>
+        <v>189.547665</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>67.62943799999999</v>
+        <v>75.97725800000001</v>
       </c>
       <c r="D35" t="n">
-        <v>285.976518</v>
+        <v>321.87069</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>422.488103</v>
+        <v>474.637797</v>
       </c>
       <c r="D36" t="n">
-        <v>167.243298</v>
+        <v>188.23474</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>421.784418</v>
+        <v>473.847253</v>
       </c>
       <c r="D37" t="n">
-        <v>285.845726</v>
+        <v>321.723481</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
